--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.4.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.4.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0004.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0004.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -871,7 +871,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.4.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>L49: suspicious token(s): sUiVRE (odd internal casing) :: cas: le symbole â†’ signifie " A sUiVRE ", le</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | suspicious token(s): sUiVRE (odd internal casing) :: cas: le symbole → signifie " A sUiVRE ", le</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -609,19 +609,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: L'exemplaire film Ã© fut reproduit grÃ¢ce Ã a la</t>
+          <t>L12: stray/suspicious non-ASCII glyph(s): U+5C0F CJK UNIFIED IDEOGRAPH-5C0F | isolated marker/symbol line :: 小</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: ï»¿L'exemplaire filmÃ© fut reproduit grÃ¢ce Ã la</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]L'exemplaire filmé fut reproduit grâce à la</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]L'exemplaire filmé fut reproduit grâce à la</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å°�</t>
+          <t>L12: stray/suspicious non-ASCII glyph(s): U+5C0F CJK UNIFIED IDEOGRAPH-5C0F | isolated marker/symbol line :: 小</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -630,9 +634,17 @@
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
-      <c r="Q2" s="1" t="inlineStr"/>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: shall contain the symbol -• (meaning "CON-</t>
+        </is>
+      </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • la dernière page qui comporte une telle</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +680,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: g Ã© n Ã© rosit Ã© de:</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2207 NABLA :: TINUED "), or the symbol ∇ (meaning " END ").</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gÃ©nÃ©rositÃ© de:</t>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • la dernière page qui comporte une telle</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -689,7 +701,11 @@
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
-      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: cas: le symbole -• signifie "A SUIVRE", le</t>
+        </is>
+      </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="1" t="inlineStr"/>
@@ -727,12 +743,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã© tails</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | suspicious token(s): sUiVRE (odd internal casing) :: cas: le symbole → signifie " A sUiVRE ", le</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: La bibliothÃ¨que des Archives</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: shall contain the symbol -• (meaning "CON-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -766,12 +782,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -782,12 +798,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å°�</t>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+2207 NABLA :: symbole ∇ signifie " FIN ".</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã©tails</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: cas: le symbole -• signifie "A SUIVRE", le</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -799,7 +815,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -835,14 +851,10 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Les images suivantes ont Ã© t Ã© reproduites avec le</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Les Images suivantes ont Ã©tÃ© reproduites avec le</t>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -890,16 +902,8 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de la nettet de l'exemplaire film Ã©, et en</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de la nettetÃ© de l'exemplaire filmÃ©, et en</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -945,16 +949,8 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: conformit Ã© avec les conditions du contrat de</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: conformitÃ© avec les conditions du contrat de</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1000,16 +996,8 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: papier est imprim Ã© e sont film Ã© s en commen Ã§ ant</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: papier est ImprimÃ©e sont filmÃ©s en commenÃ§ant</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1041,12 +1029,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1055,16 +1043,8 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: derni Ã¨ re page qui comporte une empreinte</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: derniÃ¨re page qui comporte une empreinte</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1101,7 +1081,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1110,16 +1090,8 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: originaux sont film Ã© s en commen Ã§ ant par la</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: originaux sont filmÃ©s en commenÃ§ant par la</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1165,16 +1137,8 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: premi Ã¨ re page qui comporte une empreinte</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: premiÃ¨re page qui comporte une empreinte</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1211,7 +1175,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1220,16 +1184,8 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: la derni Ã¨ re page qui comporte une telle</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: dâ€™impression ou d'illustration et en terminant par</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1266,7 +1222,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1275,16 +1231,8 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: derniers Ã¨ re image de chaque microfiche, selon le</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A8 DIAERESIS :: â€¢ la derniÃ¨re page qui comporte une telle</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1330,16 +1278,8 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã© tails</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: shall contain the symbol -â€¢ (meaning "CON-</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1385,16 +1325,8 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: film Ã© s a des taux de r Ã© duction diff Ã© rents.</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN :: Un des symboles suivants apparaÃ®tra sur la</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr"/>
@@ -1436,16 +1368,8 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: reproduit en un seul clich, il est film Ã© a partir</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: derniÃ¨re Image de chaque microfiche, selon le</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr"/>
@@ -1475,16 +1399,8 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de l'angle sup Ã© rieur gauche, de gauche a droite.</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: cas: le symbole -â€¢ signifie "A SUIVRE", le</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr"/>
@@ -1514,16 +1430,8 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'images n Ã© cessaire. Les diagrammes suivants</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: filmÃ©s Ã des taux de rÃ©duction diffÃ©rents.</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr"/>
@@ -1543,165 +1451,6 @@
       <c r="X19" s="1" t="inlineStr"/>
       <c r="Y19" s="1" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr"/>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
-      <c r="D20" s="1" t="inlineStr"/>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: illustrent la. m Ã© thode.</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: reproduit en un seul clichÃ©, II est filmÃ© Ã partir</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr"/>
-      <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
-      <c r="T20" s="1" t="inlineStr"/>
-      <c r="U20" s="1" t="inlineStr"/>
-      <c r="V20" s="1" t="inlineStr"/>
-      <c r="W20" s="1" t="inlineStr"/>
-      <c r="X20" s="1" t="inlineStr"/>
-      <c r="Y20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de l'angle supÃ©rieur gauche, de gauche Ã droite,</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
-      <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
-      <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="1" t="inlineStr"/>
-      <c r="U21" s="1" t="inlineStr"/>
-      <c r="V21" s="1" t="inlineStr"/>
-      <c r="W21" s="1" t="inlineStr"/>
-      <c r="X21" s="1" t="inlineStr"/>
-      <c r="Y21" s="1" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr"/>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr"/>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'Images nÃ©cessaire. Les diagrammes suivants</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr"/>
-      <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="1" t="inlineStr"/>
-      <c r="U22" s="1" t="inlineStr"/>
-      <c r="V22" s="1" t="inlineStr"/>
-      <c r="W22" s="1" t="inlineStr"/>
-      <c r="X22" s="1" t="inlineStr"/>
-      <c r="Y22" s="1" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr"/>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Illustrent la mÃ©thode.</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr"/>
-      <c r="M23" s="1" t="inlineStr"/>
-      <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr"/>
-      <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="1" t="inlineStr"/>
-      <c r="U23" s="1" t="inlineStr"/>
-      <c r="V23" s="1" t="inlineStr"/>
-      <c r="W23" s="1" t="inlineStr"/>
-      <c r="X23" s="1" t="inlineStr"/>
-      <c r="Y23" s="1" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr"/>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr"/>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr"/>
-      <c r="G24" s="1" t="inlineStr"/>
-      <c r="H24" s="1" t="inlineStr"/>
-      <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="inlineStr"/>
-      <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr"/>
-      <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
-      <c r="T24" s="1" t="inlineStr"/>
-      <c r="U24" s="1" t="inlineStr"/>
-      <c r="V24" s="1" t="inlineStr"/>
-      <c r="W24" s="1" t="inlineStr"/>
-      <c r="X24" s="1" t="inlineStr"/>
-      <c r="Y24" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
